--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondToStock001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBondToStock001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -47,9 +47,6 @@
     <t>正股名称</t>
   </si>
   <si>
-    <t>委托卷面总额</t>
-  </si>
-  <si>
     <t>转股价</t>
   </si>
   <si>
@@ -68,24 +65,31 @@
     <t>币种</t>
   </si>
   <si>
-    <t>委托开始日</t>
-  </si>
-  <si>
-    <t>委托结束日</t>
-  </si>
-  <si>
     <t>投资经理</t>
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>委托卷面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令开始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令结束日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -132,7 +136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -150,6 +154,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,14 +454,15 @@
     <col min="5" max="5" width="31.375" customWidth="1"/>
     <col min="6" max="6" width="15.375" customWidth="1"/>
     <col min="7" max="7" width="16.25" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="8" max="8" width="17" style="8" customWidth="1"/>
     <col min="9" max="9" width="16.125" customWidth="1"/>
     <col min="10" max="10" width="22.875" customWidth="1"/>
     <col min="11" max="11" width="23.25" customWidth="1"/>
     <col min="12" max="12" width="31" style="2" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="23.75" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -473,41 +487,42 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="H2" s="7"/>
       <c r="L2" s="4"/>
     </row>
   </sheetData>
